--- a/output/pdf_financials_xlsx/DFY.xlsx
+++ b/output/pdf_financials_xlsx/DFY.xlsx
@@ -11300,7 +11300,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">

--- a/output/pdf_financials_xlsx/DFY.xlsx
+++ b/output/pdf_financials_xlsx/DFY.xlsx
@@ -3722,13 +3722,13 @@
         <v>0</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>0</v>
+        <v>-2.7</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="127">
@@ -7776,7 +7776,11 @@
           <t>Dividends paid to non-controlling interests</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DFY.xlsx
+++ b/output/pdf_financials_xlsx/DFY.xlsx
@@ -2000,22 +2000,22 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>211.6</v>
+        <v>0</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>219.7</v>
+        <v>0</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>771.6</v>
+        <v>0</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>1229.9</v>
+        <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>1397.5</v>
+        <v>0</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>1562.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2034,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>0</v>
+        <v>572.4</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0</v>
+        <v>686.3</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0</v>
+        <v>785.5</v>
       </c>
     </row>
     <row r="61">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
